--- a/docs/01-1_요구사항정의서.xlsx
+++ b/docs/01-1_요구사항정의서.xlsx
@@ -419,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -530,6 +530,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1048,7 +1051,7 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>1. 프로젝트를 발주한 고객사(발주처) 정보를 프로젝트와 별도로 관리해야 한다.
+          <t>1. 프로젝트를 발주한 고객사(발주처) 정보를 관리해야 한다.
 2. 고객 평가를 의뢰할 고객사 담당자 정보를 관리해야 한다.</t>
         </is>
       </c>
@@ -1224,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="70.5" customHeight="1">
+    <row r="13" ht="45.5" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>URQ010</t>
@@ -1232,16 +1235,13 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>권한 및
-개인정보 보호</t>
+          <t>권한 관리</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
           <t>1. 일반 직원은 본인 정보만 조회·수정하고, 경영진만 타 직원 정보를 검색·조회한다.
-2. 주민등록번호 등 개인정보는 권한이 없는 사용자에게 그대로 노출하지 않는다.
-3. PM 권한(PM 평가, 고객 평가 의뢰·보고)은 해당 프로젝트에 PM 으로 투입된 직원에게만 준다.
-4. 로그인 비밀번호는 원문 그대로 저장하지 않는다.</t>
+2. PM 권한(PM 평가, 고객 평가 의뢰·보고)은 해당 프로젝트에 PM 으로 투입된 직원에게만 준다.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1255,59 +1255,23 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45.5" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>URQ011</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>시스템 환경</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>1. 시스템은 사내 업무용 웹 기반 시스템으로 제공한다.
-2. 데이터는 관계형 DBMS 에 저장한다.
-3. 실제 업무 시스템으로 사용할 수 있는 수준으로 설계·개발한다.</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>시스템</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
-    </row>
-    <row r="15" ht="70.5" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>URQ012</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>데이터 설계 및 적재</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>1. 데이터베이스 설계는 Information Engineering(IE) 표기법을 따른다.
-2. 화면을 만들지 않은 기능의 데이터는 별도 방법(SQL 스크립트 등)으로 적재하여 시연할 수 있어야 한다.
-3. 테이블 생성 및 테스트 데이터 삽입 SQL 은 별도 파일로 제공한다.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>기술</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="16" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>※ URQ001~URQ010 은 모두 Problem Description 문장에서 도출 (과제 일정표의 '요구사항 정의서 (“Problem Description” only!)' 에 따름). 문장별 대응은 '추적표' 시트 참고.</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="n"/>
+      <c r="C15" s="40" t="n"/>
+      <c r="D15" s="40" t="n"/>
+      <c r="E15" s="41" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="29" t="n"/>
@@ -1316,16 +1280,12 @@
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="16" t="n"/>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>※ URQ001~URQ009 는 Problem Description 문장에서 도출, URQ010 은 Problem Description 의 권한·관리 항목에서 도출, URQ011~URQ012 는 과제 개발 환경 요건(Requirements)에서 도출. 문장별 대응은 '추적표' 시트 참고.</t>
-        </is>
-      </c>
-      <c r="B17" s="40" t="n"/>
-      <c r="C17" s="40" t="n"/>
-      <c r="D17" s="40" t="n"/>
-      <c r="E17" s="41" t="n"/>
+    <row r="17" ht="19.5" customHeight="1">
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="16" t="n"/>
     </row>
     <row r="18" ht="19.5" customHeight="1">
       <c r="A18" s="29" t="n"/>
@@ -1350,8 +1310,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D4:D20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -1369,14 +1329,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1389,7 +1348,7 @@
     <row r="2">
       <c r="A2" s="34" t="inlineStr">
         <is>
-          <t>※ 회의에서 '결정 내용' 칸(노란색)을 채운 뒤, 결정된 내용은 11/09 설계 보고의 가정·비즈니스 로직에 반영</t>
+          <t>※ 문제 설명에 없는 부분은 아래 '결정 내용'과 같이 가정하여 정함. 결정 내용은 11/09 설계 보고의 가정·비즈니스 로직에 반영</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1373,8 @@
           <t>결정 내용</t>
         </is>
       </c>
-      <c r="E4" s="35" t="inlineStr">
-        <is>
-          <t>현재 구현안 (제안, 회의 참고용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="36" t="n">
         <v>1</v>
       </c>
@@ -1434,8 +1388,7 @@
           <t>URQ001</t>
         </is>
       </c>
-      <c r="D5" s="38" t="n"/>
-      <c r="E5" s="37" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>E + 입사연도 2자리 + 연도별 순번 4자리 (예: E260005). 동시 가입에도 중복되지 않게 DB 가 채번</t>
         </is>
@@ -1455,8 +1408,7 @@
           <t>URQ001, URQ002</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n"/>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>회원가입은 전 직원 가능. 프로젝트 투입은 개발자만 가능</t>
         </is>
@@ -1476,14 +1428,13 @@
           <t>URQ008</t>
         </is>
       </c>
-      <c r="D7" s="38" t="n"/>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>직급이 아니라 계정에 별도 권한(경영진)을 부여해 구분</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="36" t="n">
         <v>4</v>
       </c>
@@ -1497,10 +1448,9 @@
           <t>URQ001</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="37" t="inlineStr">
-        <is>
-          <t>DB 에는 저장하되 본인 외 화면에서는 뒷자리 마스킹. 운영 시 컬럼 암호화 권고</t>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>DB 에 저장하되 본인 외 화면에서는 뒷자리 마스킹. 실제 운영 시에는 개인정보보호법에 따라 컬럼 암호화(검색용 해시 별도)를 적용하며, 본 과제 데모에서는 생략</t>
         </is>
       </c>
     </row>
@@ -1518,8 +1468,7 @@
           <t>URQ003, URQ004</t>
         </is>
       </c>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="D9" s="42" t="inlineStr">
         <is>
           <t>프로젝트당 발주처 1곳</t>
         </is>
@@ -1539,14 +1488,13 @@
           <t>URQ005</t>
         </is>
       </c>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="D10" s="42" t="inlineStr">
         <is>
           <t>가능. 같은 기간 투입률 합계 100% 이하로 제한</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="36" t="n">
         <v>7</v>
       </c>
@@ -1560,14 +1508,13 @@
           <t>URQ005</t>
         </is>
       </c>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D11" s="42" t="inlineStr">
         <is>
           <t>기간을 나눠 다른 직무로 다시 투입하는 방식으로 표현 (투입 이력 보존)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="32" customHeight="1">
       <c r="A12" s="36" t="n">
         <v>8</v>
       </c>
@@ -1581,14 +1528,13 @@
           <t>URQ006</t>
         </is>
       </c>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="37" t="inlineStr">
+      <c r="D12" s="42" t="inlineStr">
         <is>
           <t>포함. 개발 경력 기산일(입사 전 경력 포함)로 총 경력을 계산</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="32" customHeight="1">
       <c r="A13" s="36" t="n">
         <v>9</v>
       </c>
@@ -1602,8 +1548,7 @@
           <t>URQ006</t>
         </is>
       </c>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="D13" s="42" t="inlineStr">
         <is>
           <t>초급 / 중급 / 고급 / 특급 4단계. 경력 기준 권고 등급은 자동 계산, 확정은 경영진</t>
         </is>
@@ -1623,8 +1568,7 @@
           <t>URQ007</t>
         </is>
       </c>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="37" t="inlineStr">
+      <c r="D14" s="42" t="inlineStr">
         <is>
           <t>1~5점 정수</t>
         </is>
@@ -1644,14 +1588,13 @@
           <t>URQ007</t>
         </is>
       </c>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="37" t="inlineStr">
+      <c r="D15" s="42" t="inlineStr">
         <is>
           <t>대상. 해당 프로젝트에 한 번이라도 투입된 직원은 평가 대상</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="32" customHeight="1">
       <c r="A16" s="36" t="n">
         <v>12</v>
       </c>
@@ -1665,14 +1608,13 @@
           <t>URQ004, URQ007</t>
         </is>
       </c>
-      <c r="D16" s="38" t="n"/>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="D16" s="42" t="inlineStr">
         <is>
           <t>로그인 없이 PM 이 보낸 전용 링크로 고객 담당자가 직접 입력</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="36" t="n">
         <v>13</v>
       </c>
@@ -1686,14 +1628,13 @@
           <t>URQ007</t>
         </is>
       </c>
-      <c r="D17" s="38" t="n"/>
-      <c r="E17" s="37" t="inlineStr">
-        <is>
-          <t>PM 도 동료 평가·고객 평가를 받음. PM 을 'PM 평가'하는 사람은 현재 없음 → 경영진 평가 추가 여부 결정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>PM 은 PM 평가 대상이 아님 (시나리오 정의상 PM 평가는 PM 이 팀원을 평가하는 것). PM 은 고객·동료 평가를 받으며, 종합점수는 받은 평가 유형만으로 산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="36" t="n">
         <v>14</v>
       </c>
@@ -1707,14 +1648,13 @@
           <t>URQ003</t>
         </is>
       </c>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="37" t="inlineStr">
+      <c r="D18" s="42" t="inlineStr">
         <is>
           <t>P + 착수연도 + 순번 3자리 (예: P2026-011) 자동 부여</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="32" customHeight="1">
       <c r="A19" s="36" t="n">
         <v>15</v>
       </c>
@@ -1728,8 +1668,7 @@
           <t>URQ005, URQ006</t>
         </is>
       </c>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="37" t="inlineStr">
+      <c r="D19" s="42" t="inlineStr">
         <is>
           <t>PM 고급 이상, PL·분석자·설계자 중급 이상, 프로그래머·테스터 초급 이상</t>
         </is>
@@ -1749,14 +1688,13 @@
           <t>URQ005, URQ007</t>
         </is>
       </c>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="37" t="inlineStr">
+      <c r="D20" s="42" t="inlineStr">
         <is>
           <t>같은 기간에는 1명. 기간을 나눠 교체 가능</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="36" t="n">
         <v>17</v>
       </c>
@@ -1770,14 +1708,13 @@
           <t>URQ006</t>
         </is>
       </c>
-      <c r="D21" s="38" t="n"/>
-      <c r="E21" s="37" t="inlineStr">
+      <c r="D21" s="42" t="inlineStr">
         <is>
           <t>경영진만 변경, 변경 전후 등급·처리자·사유를 이력으로 자동 기록</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="36" t="n">
         <v>18</v>
       </c>
@@ -1791,8 +1728,7 @@
           <t>URQ004</t>
         </is>
       </c>
-      <c r="D22" s="38" t="n"/>
-      <c r="E22" s="37" t="inlineStr">
+      <c r="D22" s="42" t="inlineStr">
         <is>
           <t>발주처명·사업자등록번호·업종·주소·연락처 관리, 담당자는 여러 명</t>
         </is>
@@ -1812,14 +1748,13 @@
           <t>URQ007</t>
         </is>
       </c>
-      <c r="D23" s="38" t="n"/>
-      <c r="E23" s="37" t="inlineStr">
+      <c r="D23" s="42" t="inlineStr">
         <is>
           <t>평가 항목을 별도 목록으로 관리해 항목 추가 가능</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="32" customHeight="1">
       <c r="A24" s="36" t="n">
         <v>20</v>
       </c>
@@ -1833,10 +1768,9 @@
           <t>URQ008</t>
         </is>
       </c>
-      <c r="D24" s="38" t="n"/>
-      <c r="E24" s="37" t="inlineStr">
-        <is>
-          <t>고객 40% · PM 40% · 동료 20% 가중 평균 → S/A/B/C 등급 (비율·기준은 팀 합의 필요)</t>
+      <c r="D24" s="42" t="inlineStr">
+        <is>
+          <t>고객 40% · PM 40% · 동료 20% 가중 평균으로 종합점수를 산출하고 S/A/B/C 등급 부여</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1971,7 +1905,7 @@
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>URQ001, URQ010</t>
+          <t>URQ001</t>
         </is>
       </c>
     </row>
@@ -2193,23 +2127,6 @@
       <c r="C22" s="36" t="inlineStr">
         <is>
           <t>URQ007, URQ008</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="36" t="inlineStr">
-        <is>
-          <t>과제 요건</t>
-        </is>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>웹 기반 시스템, 관계형 DBMS, IE 표기법, 생략 UI 데이터 적재</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>URQ011, URQ012</t>
         </is>
       </c>
     </row>

--- a/docs/01-1_요구사항정의서.xlsx
+++ b/docs/01-1_요구사항정의서.xlsx
@@ -7,12 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="요구사항정의_양식" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="팀 확인 필요 사항" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="추적표" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'요구사항정의_양식'!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'요구사항정의_양식'!$A$1:$E$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'요구사항정의_양식'!$A$1:$E$20</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="7">
     <font>
       <name val="돋움"/>
       <charset val="129"/>
@@ -67,27 +65,8 @@
       <sz val="14"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -106,18 +85,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -392,34 +361,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -510,28 +456,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,12 +878,12 @@
           <t>URQ001</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>직원 정보 관리</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>1. 직원 정보로 직원번호, 직원명, 주민등록번호, 최종학력을 관리해야 한다.
 2. 직원번호(사번)는 정해진 규칙에 따라 시스템이 자동으로 부여한다.
@@ -972,13 +896,13 @@
           <t>기능</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>직원, 개발자, 지원직</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="70.5" customFormat="1" customHeight="1" s="4">
+    <row r="5" ht="83" customFormat="1" customHeight="1" s="4">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>URQ002</t>
@@ -1009,7 +933,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45.5" customFormat="1" customHeight="1" s="5">
+    <row r="6" ht="58" customFormat="1" customHeight="1" s="5">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>URQ003</t>
@@ -1034,7 +958,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>프로젝트</t>
+          <t>프로젝트, 발주처</t>
         </is>
       </c>
     </row>
@@ -1066,7 +990,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="83" customFormat="1" customHeight="1" s="4">
+    <row r="8" ht="108" customFormat="1" customHeight="1" s="4">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>URQ005</t>
@@ -1127,7 +1051,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="133" customHeight="1">
+    <row r="10" ht="158" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>URQ007</t>
@@ -1162,7 +1086,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="95.5" customHeight="1">
+    <row r="11" ht="120.5" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>URQ008</t>
@@ -1180,8 +1104,8 @@
 3. 경영진은 현재 회사가 수행 중인 프로젝트 수를 조회할 수 있어야 한다.
 4. 경영진은 프로젝트별 현재 투입 인원 수, 각 인원의 직무, 투입 기간을 조회할 수 있어야 한다.
 5. 경영진은 과거 특정 시점에 직원별로 참여한 프로젝트와 직무를 조회할 수 있어야 한다.
-6. 개인별 경력관리 자료를 조회할 수 있어야 한다.
-7. 인센티브 지급을 위한 기초자료를 추출할 수 있어야 한다.</t>
+6. 경영진은 개인별 경력관리 자료를 조회할 수 있어야 한다.
+7. 경영진은 인센티브 지급을 위한 기초자료를 추출할 수 있어야 한다.</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1191,11 +1115,11 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>직원, 경영진, 프로젝트, 프로젝트투입</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="95.5" customHeight="1">
+          <t>직원, 경영진, 프로젝트, 프로젝트투입, 평가</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="108" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>URQ009</t>
@@ -1213,7 +1137,7 @@
 2. ID 중복 확인 결과(사용 가능 / 이미 등록됨)를 화면에 바로 표시한다.
 3. 로그인한 직원은 자신의 정보를 수정하는 페이지로 이동할 수 있다.
 4. 경영진으로 로그인하면 직원 검색, 프로젝트 현황, 투입 현황 조회 메뉴를 사용할 수 있다.
-5. 프로젝트 종료 후 참여 직원은 평가 입력 화면에서 항목별 평점과 평가 내용을 입력한다.</t>
+5. 프로젝트 종료 후 참여 직원은 평가 입력 화면에서 항목별 평점과 평가 내용을 입력한다(PM 평가·동료 평가). 고객 평가는 PM이 고객사 담당자에게 의뢰하고 그 결과를 회사에 보고한다.</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1227,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="45.5" customHeight="1">
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>URQ010</t>
@@ -1235,13 +1159,13 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>권한 관리</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>1. 일반 직원은 본인 정보만 조회·수정하고, 경영진만 타 직원 정보를 검색·조회한다.
-2. PM 권한(PM 평가, 고객 평가 의뢰·보고)은 해당 프로젝트에 PM 으로 투입된 직원에게만 준다.</t>
+          <t>PM 권한 관리</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>1. PM 권한(PM 평가, 고객 평가 의뢰·보고)은 해당 프로젝트에 PM으로 투입된 직원에게만 준다.
+2. PM은 자신이 PM으로 투입된 프로젝트의 팀원에 대해서만 PM 평가를 입력할 수 있다.</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1251,7 +1175,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>직원, 경영진, 프로젝트투입, 평가</t>
+          <t>프로젝트투입, 직무, PM평가, 고객평가</t>
         </is>
       </c>
     </row>
@@ -1262,16 +1186,12 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="16" t="n"/>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="39" t="inlineStr">
-        <is>
-          <t>※ URQ001~URQ010 은 모두 Problem Description 문장에서 도출 (과제 일정표의 '요구사항 정의서 (“Problem Description” only!)' 에 따름). 문장별 대응은 '추적표' 시트 참고.</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="n"/>
-      <c r="C15" s="40" t="n"/>
-      <c r="D15" s="40" t="n"/>
-      <c r="E15" s="41" t="n"/>
+    <row r="15" ht="19.5" customHeight="1">
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="16" t="n"/>
     </row>
     <row r="16" ht="19.5" customHeight="1">
       <c r="A16" s="29" t="n"/>
@@ -1309,8 +1229,7 @@
       <c r="E20" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A15:E15"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <dataValidations count="1">
@@ -1320,817 +1239,13 @@
   </dataValidations>
   <pageMargins left="0.48" right="0.46" top="0.55" bottom="0.59" header="0.3543307086614174" footer="0.32"/>
   <pageSetup orientation="landscape" paperSize="9" scale="85" pageOrder="overThenDown"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>팀 확인 필요 사항 (문제 설명에 없어서 팀이 정해야 하는 것)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>※ 문제 설명에 없는 부분은 아래 '결정 내용'과 같이 가정하여 정함. 결정 내용은 11/09 설계 보고의 가정·비즈니스 로직에 반영</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>확인할 내용</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>관련 요구사항</t>
-        </is>
-      </c>
-      <c r="D4" s="35" t="inlineStr">
-        <is>
-          <t>결정 내용</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>사번 자동 부여 규칙은? (예: 입사연도 4자리 + 순번 3자리)</t>
-        </is>
-      </c>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>URQ001</t>
-        </is>
-      </c>
-      <c r="D5" s="42" t="inlineStr">
-        <is>
-          <t>E + 입사연도 2자리 + 연도별 순번 4자리 (예: E260005). 동시 가입에도 중복되지 않게 DB 가 채번</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>마케팅·경영관리·연구개발 직원도 회원가입 대상인가? 프로젝트에 투입될 수 있는가?</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>URQ001, URQ002</t>
-        </is>
-      </c>
-      <c r="D6" s="42" t="inlineStr">
-        <is>
-          <t>회원가입은 전 직원 가능. 프로젝트 투입은 개발자만 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>경영진은 누구인가? (직급으로 구분 / 별도 권한 부여)</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>URQ008</t>
-        </is>
-      </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>직급이 아니라 계정에 별도 권한(경영진)을 부여해 구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>주민등록번호는 어떻게 저장하나? (암호화, 화면 마스킹 등)</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>URQ001</t>
-        </is>
-      </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>DB 에 저장하되 본인 외 화면에서는 뒷자리 마스킹. 실제 운영 시에는 개인정보보호법에 따라 컬럼 암호화(검색용 해시 별도)를 적용하며, 본 과제 데모에서는 생략</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>한 프로젝트의 발주처는 1곳뿐인가?</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>URQ003, URQ004</t>
-        </is>
-      </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>프로젝트당 발주처 1곳</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>한 직원이 같은 기간에 여러 프로젝트에 동시 투입될 수 있는가?</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>URQ005</t>
-        </is>
-      </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>가능. 같은 기간 투입률 합계 100% 이하로 제한</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>한 직원이 한 프로젝트에서 직무가 바뀔 수 있는가? (예: 프로그래머 → PL)</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>URQ005</t>
-        </is>
-      </c>
-      <c r="D11" s="42" t="inlineStr">
-        <is>
-          <t>기간을 나눠 다른 직무로 다시 투입하는 방식으로 표현 (투입 이력 보존)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>경력은 우리 회사 프로젝트 경력만인가, 입사 전 타사 경력도 포함하나?</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>URQ006</t>
-        </is>
-      </c>
-      <c r="D12" s="42" t="inlineStr">
-        <is>
-          <t>포함. 개발 경력 기산일(입사 전 경력 포함)로 총 경력을 계산</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>기술 등급 기준은? (예: 초급/중급/고급/특급)</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>URQ006</t>
-        </is>
-      </c>
-      <c r="D13" s="42" t="inlineStr">
-        <is>
-          <t>초급 / 중급 / 고급 / 특급 4단계. 경력 기준 권고 등급은 자동 계산, 확정은 경영진</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>평점 척도는? (예: 1~5점, 100점 만점)</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-      <c r="D14" s="42" t="inlineStr">
-        <is>
-          <t>1~5점 정수</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>일정 기간만 투입되고 중간에 빠진 직원도 종료 시점 평가 대상인가?</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-      <c r="D15" s="42" t="inlineStr">
-        <is>
-          <t>대상. 해당 프로젝트에 한 번이라도 투입된 직원은 평가 대상</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>고객사 담당자는 시스템에 로그인해서 평가를 입력하나, PM이 대신 입력하나?</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>URQ004, URQ007</t>
-        </is>
-      </c>
-      <c r="D16" s="42" t="inlineStr">
-        <is>
-          <t>로그인 없이 PM 이 보낸 전용 링크로 고객 담당자가 직접 입력</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>PM도 동료 평가를 받는가? PM은 누가 평가하는가?</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-      <c r="D17" s="42" t="inlineStr">
-        <is>
-          <t>PM 은 PM 평가 대상이 아님 (시나리오 정의상 PM 평가는 PM 이 팀원을 평가하는 것). PM 은 고객·동료 평가를 받으며, 종합점수는 받은 평가 유형만으로 산출</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>프로젝트번호도 자동으로 부여하는가, 직접 입력하는가?</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>URQ003</t>
-        </is>
-      </c>
-      <c r="D18" s="42" t="inlineStr">
-        <is>
-          <t>P + 착수연도 + 순번 3자리 (예: P2026-011) 자동 부여</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>기술 등급에 따라 맡을 수 있는 직무를 제한하는가? (예: PM 은 고급 이상)</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>URQ005, URQ006</t>
-        </is>
-      </c>
-      <c r="D19" s="42" t="inlineStr">
-        <is>
-          <t>PM 고급 이상, PL·분석자·설계자 중급 이상, 프로그래머·테스터 초급 이상</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>한 프로젝트의 PM 은 한 명인가? 프로젝트 중간에 바뀔 수 있는가?</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="inlineStr">
-        <is>
-          <t>URQ005, URQ007</t>
-        </is>
-      </c>
-      <c r="D20" s="42" t="inlineStr">
-        <is>
-          <t>같은 기간에는 1명. 기간을 나눠 교체 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>기술 등급은 누가 바꾸며, 변경 이력을 남기는가?</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
-        <is>
-          <t>URQ006</t>
-        </is>
-      </c>
-      <c r="D21" s="42" t="inlineStr">
-        <is>
-          <t>경영진만 변경, 변경 전후 등급·처리자·사유를 이력으로 자동 기록</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>발주처에서 관리할 정보는 무엇이고, 한 발주처에 담당자가 여러 명일 수 있는가?</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="inlineStr">
-        <is>
-          <t>URQ004</t>
-        </is>
-      </c>
-      <c r="D22" s="42" t="inlineStr">
-        <is>
-          <t>발주처명·사업자등록번호·업종·주소·연락처 관리, 담당자는 여러 명</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="37" t="inlineStr">
-        <is>
-          <t>평가 항목(업무수행, 커뮤니케이션)이 나중에 늘어날 수 있는가?</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-      <c r="D23" s="42" t="inlineStr">
-        <is>
-          <t>평가 항목을 별도 목록으로 관리해 항목 추가 가능</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>인센티브 기초자료는 어떤 형태이며, 고객·PM·동료 평가를 어떻게 합산하는가?</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="inlineStr">
-        <is>
-          <t>URQ008</t>
-        </is>
-      </c>
-      <c r="D24" s="42" t="inlineStr">
-        <is>
-          <t>고객 40% · PM 40% · 동료 20% 가중 평균으로 종합점수를 산출하고 S/A/B/C 등급 부여</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="33" t="inlineStr">
-        <is>
-          <t>요구사항 추적표 (Problem Description 문장 → 요구사항 ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="34" t="inlineStr">
-        <is>
-          <t>¶1 회사와 투입 · ¶2 관리 정보와 회원가입 · ¶3 경영진 조회 · ¶4 평가 개요 · ¶5 평가 종류별 설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>문단</t>
-        </is>
-      </c>
-      <c r="B4" s="35" t="inlineStr">
-        <is>
-          <t>Problem Description 원문 요지</t>
-        </is>
-      </c>
-      <c r="C4" s="35" t="inlineStr">
-        <is>
-          <t>요구사항 ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
-        <is>
-          <t>¶1</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>100명 중 개발자 70명이 월평균 10개 정도의 프로젝트를 수행</t>
-        </is>
-      </c>
-      <c r="C5" s="36" t="inlineStr">
-        <is>
-          <t>URQ001, URQ003</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>¶1</t>
-        </is>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>프로젝트 초기부터 종료 시까지 또는 일정 기간만 투입</t>
-        </is>
-      </c>
-      <c r="C6" s="36" t="inlineStr">
-        <is>
-          <t>URQ005</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
-        <is>
-          <t>¶1</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>경력과 기술 등급에 따라 PM, PL, 분석자, 설계자, 프로그래머, 테스터 직무</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>URQ005, URQ006</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>프로젝트번호, 프로젝트명, 착수일자/종료일자, 발주처 관리</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>URQ003, URQ004</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>직원번호, 직원명, 주민등록번호, 최종학력 관리</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>URQ001</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>투입 직원의 경력과 경험한 기술(Skill Set) 관리</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="inlineStr">
-        <is>
-          <t>URQ006</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>회원가입 페이지로 자신의 정보를 저장하고 수정/변경</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="inlineStr">
-        <is>
-          <t>URQ001, URQ002, URQ009</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>직원 사번은 정해진 규칙에 따라 자동 부여</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="inlineStr">
-        <is>
-          <t>URQ001</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
-        <is>
-          <t>¶2</t>
-        </is>
-      </c>
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>로그인 ID 중복 체크, 중복 시 에러 메시지 후 새 ID 입력</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="inlineStr">
-        <is>
-          <t>URQ002, URQ009</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
-        <is>
-          <t>¶3</t>
-        </is>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>현재 몇 개의 프로젝트를 수행 중인지, 프로젝트별 투입 인원·직무·투입 기간</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr">
-        <is>
-          <t>URQ008</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>¶3</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>과거 특정 시점에 어떤 직원이 어느 프로젝트에 어떤 직무로 참여했는지</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="inlineStr">
-        <is>
-          <t>URQ005, URQ008</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>¶3</t>
-        </is>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>개인별 경력관리와 인센티브 지급을 위한 기초자료 추출</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="inlineStr">
-        <is>
-          <t>URQ006, URQ008</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>¶3</t>
-        </is>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>경영진은 타 직원 정보를 검색할 수 있는 권한</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="inlineStr">
-        <is>
-          <t>URQ008, URQ010</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
-        <is>
-          <t>¶4</t>
-        </is>
-      </c>
-      <c r="B18" s="37" t="inlineStr">
-        <is>
-          <t>프로젝트 종료 시점 평가: 고객 평가, PM 평가, 동료 평가</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="36" t="inlineStr">
-        <is>
-          <t>¶4</t>
-        </is>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>평가자와 피평가자, 평가 항목(업무수행, 커뮤니케이션)별 평점과 평가 내용</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="36" t="inlineStr">
-        <is>
-          <t>¶5</t>
-        </is>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>고객 평가: PM 이 주관하여 고객사 담당자에게 의뢰하고 결과를 회사에 보고</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="inlineStr">
-        <is>
-          <t>URQ004, URQ007, URQ010</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="36" t="inlineStr">
-        <is>
-          <t>¶5</t>
-        </is>
-      </c>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>동료 평가: 자기 이외의 참여자 평가 / PM 평가: PM 이 팀원 평가</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="inlineStr">
-        <is>
-          <t>URQ007</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="36" t="inlineStr">
-        <is>
-          <t>¶5</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>평가 결과는 인사고과와 인사 평가의 근거 자료</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="inlineStr">
-        <is>
-          <t>URQ007, URQ008</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;C&amp;N페이지 중 &amp;P페이지&amp;R</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>